--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/80.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/80.xlsx
@@ -426,13 +426,13 @@
         <v>-6.108911098752638</v>
       </c>
       <c r="E2">
-        <v>-17.68985180131078</v>
+        <v>-15.27489359707831</v>
       </c>
       <c r="F2">
-        <v>-2.378527919071451</v>
+        <v>-0.6148483966688156</v>
       </c>
       <c r="G2">
-        <v>-15.12835338657068</v>
+        <v>-14.5439229192499</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.584674083489618</v>
       </c>
       <c r="E3">
-        <v>-17.86884879341197</v>
+        <v>-15.17276745125733</v>
       </c>
       <c r="F3">
-        <v>-2.200998844242684</v>
+        <v>-0.7558522676059446</v>
       </c>
       <c r="G3">
-        <v>-14.90160584622215</v>
+        <v>-14.18919299889869</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.018955707729948</v>
       </c>
       <c r="E4">
-        <v>-18.45887272881935</v>
+        <v>-15.8567119375838</v>
       </c>
       <c r="F4">
-        <v>-1.737601007075209</v>
+        <v>-0.3336334023990367</v>
       </c>
       <c r="G4">
-        <v>-15.84674673441084</v>
+        <v>-14.47046191373348</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.444577714923616</v>
       </c>
       <c r="E5">
-        <v>-19.95103208519078</v>
+        <v>-16.76812167331555</v>
       </c>
       <c r="F5">
-        <v>-1.638902687766454</v>
+        <v>-0.04613109954200942</v>
       </c>
       <c r="G5">
-        <v>-14.9136777505311</v>
+        <v>-12.88946123327143</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.835911733369525</v>
       </c>
       <c r="E6">
-        <v>-20.48511125270741</v>
+        <v>-17.49075291308954</v>
       </c>
       <c r="F6">
-        <v>-1.721540619869733</v>
+        <v>-0.3557557822582002</v>
       </c>
       <c r="G6">
-        <v>-13.82056209782807</v>
+        <v>-13.11322762736185</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.1850481009918</v>
       </c>
       <c r="E7">
-        <v>-20.0796860317487</v>
+        <v>-17.51892454989126</v>
       </c>
       <c r="F7">
-        <v>-1.65070775162375</v>
+        <v>-0.06526224470966401</v>
       </c>
       <c r="G7">
-        <v>-13.28862033003244</v>
+        <v>-12.5433999764148</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.477429498317087</v>
       </c>
       <c r="E8">
-        <v>-21.26317101433529</v>
+        <v>-18.68134307139417</v>
       </c>
       <c r="F8">
-        <v>-1.324623408613933</v>
+        <v>0.3154065399402236</v>
       </c>
       <c r="G8">
-        <v>-11.9847719010271</v>
+        <v>-11.73200512801267</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.72136449924696</v>
       </c>
       <c r="E9">
-        <v>-21.81451725324316</v>
+        <v>-19.5069518101026</v>
       </c>
       <c r="F9">
-        <v>-1.441520959762193</v>
+        <v>0.1424392843986728</v>
       </c>
       <c r="G9">
-        <v>-11.90773550632826</v>
+        <v>-11.27447449230323</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.9241969772251774</v>
       </c>
       <c r="E10">
-        <v>-22.74414051143377</v>
+        <v>-20.76362146112715</v>
       </c>
       <c r="F10">
-        <v>-1.571346012598543</v>
+        <v>-0.1310255044505139</v>
       </c>
       <c r="G10">
-        <v>-11.1095563557189</v>
+        <v>-9.9777669100261</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.116991458895045</v>
       </c>
       <c r="E11">
-        <v>-22.43614088027607</v>
+        <v>-20.90734164070858</v>
       </c>
       <c r="F11">
-        <v>-0.9059516126258123</v>
+        <v>0.5778142806968426</v>
       </c>
       <c r="G11">
-        <v>-10.37955126939975</v>
+        <v>-9.252654810013992</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.6672534737848393</v>
       </c>
       <c r="E12">
-        <v>-24.85676420549214</v>
+        <v>-21.55745389772375</v>
       </c>
       <c r="F12">
-        <v>-0.7559276490395994</v>
+        <v>0.6253832788026042</v>
       </c>
       <c r="G12">
-        <v>-10.20864435593487</v>
+        <v>-8.738685993951062</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.391929951454739</v>
       </c>
       <c r="E13">
-        <v>-24.81757931990377</v>
+        <v>-22.42955195059491</v>
       </c>
       <c r="F13">
-        <v>-0.6125513338608526</v>
+        <v>0.2790428676921309</v>
       </c>
       <c r="G13">
-        <v>-8.742403736591664</v>
+        <v>-7.458094147359103</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.019868220743473</v>
       </c>
       <c r="E14">
-        <v>-24.57207715852594</v>
+        <v>-22.60298797661468</v>
       </c>
       <c r="F14">
-        <v>-0.9513088697660992</v>
+        <v>0.6653213563937768</v>
       </c>
       <c r="G14">
-        <v>-8.435204973820532</v>
+        <v>-7.559482915044822</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.533805165170534</v>
       </c>
       <c r="E15">
-        <v>-27.37430140294636</v>
+        <v>-25.11488269545534</v>
       </c>
       <c r="F15">
-        <v>-0.3861021936923573</v>
+        <v>1.026680896884408</v>
       </c>
       <c r="G15">
-        <v>-7.836522607953192</v>
+        <v>-6.352759271070621</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.924239076121328</v>
       </c>
       <c r="E16">
-        <v>-28.09689188645429</v>
+        <v>-23.99662585247523</v>
       </c>
       <c r="F16">
-        <v>-0.3663671686880619</v>
+        <v>1.036692545314643</v>
       </c>
       <c r="G16">
-        <v>-6.882085707890231</v>
+        <v>-6.713731225036134</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.200027617775564</v>
       </c>
       <c r="E17">
-        <v>-28.18959427786531</v>
+        <v>-25.47780365937806</v>
       </c>
       <c r="F17">
-        <v>-0.2539809064154473</v>
+        <v>1.547652753648656</v>
       </c>
       <c r="G17">
-        <v>-7.400321817153282</v>
+        <v>-6.209293469580765</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.378782501415896</v>
       </c>
       <c r="E18">
-        <v>-29.17598648621606</v>
+        <v>-26.47816621004248</v>
       </c>
       <c r="F18">
-        <v>-0.08364123227557663</v>
+        <v>1.77823213368751</v>
       </c>
       <c r="G18">
-        <v>-6.495678832546497</v>
+        <v>-5.702839591891981</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.481740252358822</v>
       </c>
       <c r="E19">
-        <v>-30.30508223173354</v>
+        <v>-27.62868843032724</v>
       </c>
       <c r="F19">
-        <v>0.7717375747944153</v>
+        <v>1.678736924937261</v>
       </c>
       <c r="G19">
-        <v>-5.834519851262031</v>
+        <v>-4.79263820132476</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.53557267740203</v>
       </c>
       <c r="E20">
-        <v>-30.17206057199522</v>
+        <v>-27.78076364445283</v>
       </c>
       <c r="F20">
-        <v>0.7712770025184588</v>
+        <v>1.828856979142199</v>
       </c>
       <c r="G20">
-        <v>-6.087018470087783</v>
+        <v>-4.621943162774398</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.559399343341636</v>
       </c>
       <c r="E21">
-        <v>-31.15543681665687</v>
+        <v>-27.58229421411866</v>
       </c>
       <c r="F21">
-        <v>0.7687372280614755</v>
+        <v>2.291336156859968</v>
       </c>
       <c r="G21">
-        <v>-6.327483255878286</v>
+        <v>-5.14453594996713</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.572547634045411</v>
       </c>
       <c r="E22">
-        <v>-31.70255798931559</v>
+        <v>-28.78209528855489</v>
       </c>
       <c r="F22">
-        <v>0.869629064252844</v>
+        <v>2.288556155856173</v>
       </c>
       <c r="G22">
-        <v>-5.737212986226233</v>
+        <v>-4.692831874406813</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.584348923964525</v>
       </c>
       <c r="E23">
-        <v>-31.88197612949949</v>
+        <v>-29.13630346848685</v>
       </c>
       <c r="F23">
-        <v>0.6584011751107897</v>
+        <v>2.563695075226418</v>
       </c>
       <c r="G23">
-        <v>-5.422618464720371</v>
+        <v>-3.946161501842971</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.602448177989268</v>
       </c>
       <c r="E24">
-        <v>-31.77845747792115</v>
+        <v>-30.18185566127381</v>
       </c>
       <c r="F24">
-        <v>1.419196163761731</v>
+        <v>2.668085935327211</v>
       </c>
       <c r="G24">
-        <v>-6.371884292650991</v>
+        <v>-4.631709272115248</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.629539206176317</v>
       </c>
       <c r="E25">
-        <v>-31.70088245393275</v>
+        <v>-28.67899099234825</v>
       </c>
       <c r="F25">
-        <v>0.8782275178939029</v>
+        <v>2.524839673830704</v>
       </c>
       <c r="G25">
-        <v>-4.418198948105492</v>
+        <v>-4.819066286364762</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.661897812692274</v>
       </c>
       <c r="E26">
-        <v>-32.26026673420424</v>
+        <v>-28.87523694194465</v>
       </c>
       <c r="F26">
-        <v>0.8475481027638204</v>
+        <v>2.59325288089311</v>
       </c>
       <c r="G26">
-        <v>-6.370013834421303</v>
+        <v>-4.819675426743988</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.695847896332206</v>
       </c>
       <c r="E27">
-        <v>-32.18782926397754</v>
+        <v>-30.40862578991892</v>
       </c>
       <c r="F27">
-        <v>1.150298164404178</v>
+        <v>2.432349139838528</v>
       </c>
       <c r="G27">
-        <v>-6.259332365406849</v>
+        <v>-4.743314383335159</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.718260517422674</v>
       </c>
       <c r="E28">
-        <v>-31.83219461473317</v>
+        <v>-30.3123798675969</v>
       </c>
       <c r="F28">
-        <v>1.277522143595737</v>
+        <v>2.831728259015448</v>
       </c>
       <c r="G28">
-        <v>-6.038038948834267</v>
+        <v>-4.590701544520297</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.718805156088131</v>
       </c>
       <c r="E29">
-        <v>-31.87417809725828</v>
+        <v>-29.42726245195368</v>
       </c>
       <c r="F29">
-        <v>1.288085484716237</v>
+        <v>2.833472800765744</v>
       </c>
       <c r="G29">
-        <v>-6.396220112910173</v>
+        <v>-5.383888392456437</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.682660162160797</v>
       </c>
       <c r="E30">
-        <v>-31.92594534787697</v>
+        <v>-29.17995342944679</v>
       </c>
       <c r="F30">
-        <v>1.29048609344955</v>
+        <v>2.120530111872322</v>
       </c>
       <c r="G30">
-        <v>-7.66905535130362</v>
+        <v>-5.644868628953803</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.596202453036742</v>
       </c>
       <c r="E31">
-        <v>-29.97235033978295</v>
+        <v>-27.98815416858211</v>
       </c>
       <c r="F31">
-        <v>1.076455837383825</v>
+        <v>2.274556746748861</v>
       </c>
       <c r="G31">
-        <v>-7.13832524317536</v>
+        <v>-6.081489859037201</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.450379843986799</v>
       </c>
       <c r="E32">
-        <v>-30.74843115826948</v>
+        <v>-28.25132643553787</v>
       </c>
       <c r="F32">
-        <v>0.933086977511703</v>
+        <v>2.437559570802137</v>
       </c>
       <c r="G32">
-        <v>-6.750984793989552</v>
+        <v>-5.430659779835261</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.236244579075162</v>
       </c>
       <c r="E33">
-        <v>-29.42190979567661</v>
+        <v>-27.08801580465545</v>
       </c>
       <c r="F33">
-        <v>0.9537100123717994</v>
+        <v>2.549076047301812</v>
       </c>
       <c r="G33">
-        <v>-7.063189101616061</v>
+        <v>-6.071667470422184</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.954902120801638</v>
       </c>
       <c r="E34">
-        <v>-30.46034096308651</v>
+        <v>-27.48519014597218</v>
       </c>
       <c r="F34">
-        <v>0.9263871419578605</v>
+        <v>2.508254101691852</v>
       </c>
       <c r="G34">
-        <v>-6.986768468387525</v>
+        <v>-5.552458060770586</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.607891845364529</v>
       </c>
       <c r="E35">
-        <v>-28.99166853715587</v>
+        <v>-27.27589313428568</v>
       </c>
       <c r="F35">
-        <v>1.13520199685556</v>
+        <v>2.042534350694331</v>
       </c>
       <c r="G35">
-        <v>-7.503610837978543</v>
+        <v>-6.711675376256246</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.203979350641902</v>
       </c>
       <c r="E36">
-        <v>-26.92523074950172</v>
+        <v>-27.58254328018908</v>
       </c>
       <c r="F36">
-        <v>1.097907239646721</v>
+        <v>2.309349834401246</v>
       </c>
       <c r="G36">
-        <v>-8.255389382309479</v>
+        <v>-5.742241704900386</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.752564188530476</v>
       </c>
       <c r="E37">
-        <v>-26.46429549415699</v>
+        <v>-25.3707912901028</v>
       </c>
       <c r="F37">
-        <v>1.061694330265937</v>
+        <v>1.907976006518385</v>
       </c>
       <c r="G37">
-        <v>-8.78620556462176</v>
+        <v>-6.346548687638949</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.262048228317044</v>
       </c>
       <c r="E38">
-        <v>-27.95401400303828</v>
+        <v>-24.68773891315584</v>
       </c>
       <c r="F38">
-        <v>1.078535039564851</v>
+        <v>2.438159308801764</v>
       </c>
       <c r="G38">
-        <v>-8.204158690089258</v>
+        <v>-6.38942356291805</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7455866622595528</v>
       </c>
       <c r="E39">
-        <v>-25.30854741486737</v>
+        <v>-23.37974353772835</v>
       </c>
       <c r="F39">
-        <v>0.6463128096017365</v>
+        <v>2.61468771580795</v>
       </c>
       <c r="G39">
-        <v>-8.231199226054025</v>
+        <v>-6.301316703935886</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.21073332202615</v>
       </c>
       <c r="E40">
-        <v>-24.05402426052245</v>
+        <v>-23.89072295933185</v>
       </c>
       <c r="F40">
-        <v>0.8215042316198039</v>
+        <v>2.502609606209177</v>
       </c>
       <c r="G40">
-        <v>-7.612987952050523</v>
+        <v>-6.97261919675268</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3296873880515941</v>
       </c>
       <c r="E41">
-        <v>-25.37520202378627</v>
+        <v>-23.00972192656161</v>
       </c>
       <c r="F41">
-        <v>1.12076520975957</v>
+        <v>2.123792222704546</v>
       </c>
       <c r="G41">
-        <v>-8.018211968239473</v>
+        <v>-6.633215446975519</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8680422049144252</v>
       </c>
       <c r="E42">
-        <v>-23.18269604823259</v>
+        <v>-21.42267745430746</v>
       </c>
       <c r="F42">
-        <v>1.297600112704792</v>
+        <v>2.623610889470906</v>
       </c>
       <c r="G42">
-        <v>-8.847487073099209</v>
+        <v>-7.169275533422006</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.398261231687984</v>
       </c>
       <c r="E43">
-        <v>-23.61408301067728</v>
+        <v>-21.2259243156222</v>
       </c>
       <c r="F43">
-        <v>0.8122397705868943</v>
+        <v>2.56347969970169</v>
       </c>
       <c r="G43">
-        <v>-9.232377718585957</v>
+        <v>-6.858888715296557</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.910536509633536</v>
       </c>
       <c r="E44">
-        <v>-23.24383497581015</v>
+        <v>-21.40063284283812</v>
       </c>
       <c r="F44">
-        <v>0.9837880327674495</v>
+        <v>2.188621912382441</v>
       </c>
       <c r="G44">
-        <v>-9.056604303178352</v>
+        <v>-7.092119959083751</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.402449233316737</v>
       </c>
       <c r="E45">
-        <v>-22.37951684128416</v>
+        <v>-20.6569079711364</v>
       </c>
       <c r="F45">
-        <v>1.28693239729154</v>
+        <v>2.359436241044116</v>
       </c>
       <c r="G45">
-        <v>-8.937461079765521</v>
+        <v>-7.028630316731609</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.86465142845535</v>
       </c>
       <c r="E46">
-        <v>-21.40629796382172</v>
+        <v>-19.43243577030638</v>
       </c>
       <c r="F46">
-        <v>1.32487825127898</v>
+        <v>2.604861621675942</v>
       </c>
       <c r="G46">
-        <v>-8.084267283384552</v>
+        <v>-8.325049881546823</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.295015859811626</v>
       </c>
       <c r="E47">
-        <v>-21.88027069583454</v>
+        <v>-19.07326891133602</v>
       </c>
       <c r="F47">
-        <v>1.362807537918363</v>
+        <v>2.117985367210921</v>
       </c>
       <c r="G47">
-        <v>-9.227395347549352</v>
+        <v>-7.331531991392765</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.691574641413014</v>
       </c>
       <c r="E48">
-        <v>-20.25804903748881</v>
+        <v>-18.97195336236241</v>
       </c>
       <c r="F48">
-        <v>1.088972468840125</v>
+        <v>2.786820805374882</v>
       </c>
       <c r="G48">
-        <v>-9.216156045443528</v>
+        <v>-8.122143234899353</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.051171156007534</v>
       </c>
       <c r="E49">
-        <v>-21.07264905588458</v>
+        <v>-18.31243093635931</v>
       </c>
       <c r="F49">
-        <v>1.087443302614557</v>
+        <v>2.119671923243021</v>
       </c>
       <c r="G49">
-        <v>-9.01932424986062</v>
+        <v>-7.558728110661868</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.379312123733444</v>
       </c>
       <c r="E50">
-        <v>-18.67999358613989</v>
+        <v>-17.72361610351197</v>
       </c>
       <c r="F50">
-        <v>1.174748256665208</v>
+        <v>2.23428152362475</v>
       </c>
       <c r="G50">
-        <v>-9.694781477329199</v>
+        <v>-8.584133175450187</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.673830958184504</v>
       </c>
       <c r="E51">
-        <v>-17.81867782988099</v>
+        <v>-17.04131998172429</v>
       </c>
       <c r="F51">
-        <v>1.416778987680362</v>
+        <v>2.707102039999068</v>
       </c>
       <c r="G51">
-        <v>-9.712188325774687</v>
+        <v>-8.117078100224269</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.940862149206437</v>
       </c>
       <c r="E52">
-        <v>-17.3454930523455</v>
+        <v>-16.37733700882363</v>
       </c>
       <c r="F52">
-        <v>0.9976151414549789</v>
+        <v>2.390677289273296</v>
       </c>
       <c r="G52">
-        <v>-9.739357973015485</v>
+        <v>-7.962425965357215</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.182573214785402</v>
       </c>
       <c r="E53">
-        <v>-17.16127020123946</v>
+        <v>-16.32900007726576</v>
       </c>
       <c r="F53">
-        <v>1.366528564291739</v>
+        <v>2.055935678536822</v>
       </c>
       <c r="G53">
-        <v>-9.18548384102218</v>
+        <v>-7.460418150327671</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.398900349007885</v>
       </c>
       <c r="E54">
-        <v>-16.71423736109828</v>
+        <v>-15.99743426737215</v>
       </c>
       <c r="F54">
-        <v>0.7101393463548412</v>
+        <v>2.582283639745239</v>
       </c>
       <c r="G54">
-        <v>-9.997239538888094</v>
+        <v>-8.075454611159012</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.595091167779569</v>
       </c>
       <c r="E55">
-        <v>-15.74351820128807</v>
+        <v>-15.43137501641336</v>
       </c>
       <c r="F55">
-        <v>1.090311110563049</v>
+        <v>2.290141651065131</v>
       </c>
       <c r="G55">
-        <v>-10.14889231949657</v>
+        <v>-8.330853267877165</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.765590808710099</v>
       </c>
       <c r="E56">
-        <v>-15.52681260612501</v>
+        <v>-14.39939466022738</v>
       </c>
       <c r="F56">
-        <v>0.7592590482386435</v>
+        <v>1.892439147511478</v>
       </c>
       <c r="G56">
-        <v>-9.926536217805879</v>
+        <v>-8.201887655849317</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.914279086219462</v>
       </c>
       <c r="E57">
-        <v>-15.47990667235356</v>
+        <v>-13.77860427241188</v>
       </c>
       <c r="F57">
-        <v>1.142657303480755</v>
+        <v>2.499692096216517</v>
       </c>
       <c r="G57">
-        <v>-10.06954185346578</v>
+        <v>-8.782474579799002</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.03837106948114</v>
       </c>
       <c r="E58">
-        <v>-15.45357359599896</v>
+        <v>-13.31466663880006</v>
       </c>
       <c r="F58">
-        <v>1.062360337657788</v>
+        <v>1.953256225490212</v>
       </c>
       <c r="G58">
-        <v>-9.864791232952932</v>
+        <v>-9.629090322193441</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.134740435477731</v>
       </c>
       <c r="E59">
-        <v>-14.45672514116449</v>
+        <v>-13.2800328695894</v>
       </c>
       <c r="F59">
-        <v>0.5938804664741391</v>
+        <v>2.335918890478638</v>
       </c>
       <c r="G59">
-        <v>-10.23332778347568</v>
+        <v>-9.275212867318587</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.206429081595328</v>
       </c>
       <c r="E60">
-        <v>-14.12513216042684</v>
+        <v>-13.20668064761316</v>
       </c>
       <c r="F60">
-        <v>1.147050964185204</v>
+        <v>2.061956252820369</v>
       </c>
       <c r="G60">
-        <v>-10.64937066248697</v>
+        <v>-9.511003162807638</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.246215228787428</v>
       </c>
       <c r="E61">
-        <v>-14.18971725672423</v>
+        <v>-13.17042115623374</v>
       </c>
       <c r="F61">
-        <v>1.571748304661288</v>
+        <v>2.388217038086982</v>
       </c>
       <c r="G61">
-        <v>-10.84683808281341</v>
+        <v>-9.41850983098594</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.258643539705433</v>
       </c>
       <c r="E62">
-        <v>-13.01202872086745</v>
+        <v>-12.12881326430746</v>
       </c>
       <c r="F62">
-        <v>0.5484254619803217</v>
+        <v>2.175548618031459</v>
       </c>
       <c r="G62">
-        <v>-10.28769025177605</v>
+        <v>-9.432894151354073</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.240505870887424</v>
       </c>
       <c r="E63">
-        <v>-13.10773801901957</v>
+        <v>-12.0712156034039</v>
       </c>
       <c r="F63">
-        <v>0.7217041836653251</v>
+        <v>1.66370205657645</v>
       </c>
       <c r="G63">
-        <v>-10.9656568727634</v>
+        <v>-8.9009490730129</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.190333561664926</v>
       </c>
       <c r="E64">
-        <v>-12.93580997484435</v>
+        <v>-11.85444208113073</v>
       </c>
       <c r="F64">
-        <v>0.6534152317133395</v>
+        <v>1.938327388156959</v>
       </c>
       <c r="G64">
-        <v>-11.20260916973673</v>
+        <v>-9.635267800169721</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.113353853719465</v>
       </c>
       <c r="E65">
-        <v>-13.04890861318592</v>
+        <v>-12.12492783360888</v>
       </c>
       <c r="F65">
-        <v>0.09171420648824512</v>
+        <v>2.074297270387275</v>
       </c>
       <c r="G65">
-        <v>-10.80059969326641</v>
+        <v>-9.713155005072155</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.004883451374504</v>
       </c>
       <c r="E66">
-        <v>-13.03914522322538</v>
+        <v>-11.45652054160272</v>
       </c>
       <c r="F66">
-        <v>0.5349570363782046</v>
+        <v>2.006790297263533</v>
       </c>
       <c r="G66">
-        <v>-10.70778854907295</v>
+        <v>-8.959476207601675</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.872817561815816</v>
       </c>
       <c r="E67">
-        <v>-13.96379621695556</v>
+        <v>-11.57453257424261</v>
       </c>
       <c r="F67">
-        <v>0.5357588960241145</v>
+        <v>1.905953133320749</v>
       </c>
       <c r="G67">
-        <v>-10.47753348572556</v>
+        <v>-9.989317403412617</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.716977808603191</v>
       </c>
       <c r="E68">
-        <v>-13.22903772378903</v>
+        <v>-11.23919454550062</v>
       </c>
       <c r="F68">
-        <v>0.06859447227611092</v>
+        <v>1.612063289420735</v>
       </c>
       <c r="G68">
-        <v>-9.611504704288832</v>
+        <v>-9.283307151162104</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.53857214131538</v>
       </c>
       <c r="E69">
-        <v>-13.33842754191831</v>
+        <v>-10.76903931707627</v>
       </c>
       <c r="F69">
-        <v>0.1990391439297547</v>
+        <v>1.877434100377167</v>
       </c>
       <c r="G69">
-        <v>-10.59167778537409</v>
+        <v>-9.797898349786418</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.34410692632045</v>
       </c>
       <c r="E70">
-        <v>-13.99197238223129</v>
+        <v>-11.57878933980982</v>
       </c>
       <c r="F70">
-        <v>0.5892913110626298</v>
+        <v>1.71466156246187</v>
       </c>
       <c r="G70">
-        <v>-10.02657097236604</v>
+        <v>-9.670051702150843</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.130312054302157</v>
       </c>
       <c r="E71">
-        <v>-12.3405511234841</v>
+        <v>-10.4271078301791</v>
       </c>
       <c r="F71">
-        <v>0.6488070238515659</v>
+        <v>1.200369660433797</v>
       </c>
       <c r="G71">
-        <v>-10.13462055767677</v>
+        <v>-8.84812600838829</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.905524403192491</v>
       </c>
       <c r="E72">
-        <v>-13.67786383963725</v>
+        <v>-11.29874850717549</v>
       </c>
       <c r="F72">
-        <v>0.2406861434729026</v>
+        <v>1.617086509351311</v>
       </c>
       <c r="G72">
-        <v>-10.02229705807484</v>
+        <v>-9.370252008659984</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.670064980560769</v>
       </c>
       <c r="E73">
-        <v>-12.98189172634641</v>
+        <v>-11.38975272083363</v>
       </c>
       <c r="F73">
-        <v>0.4295315453913143</v>
+        <v>1.931874406089151</v>
       </c>
       <c r="G73">
-        <v>-9.862526819804069</v>
+        <v>-8.247083223551448</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.425699623148196</v>
       </c>
       <c r="E74">
-        <v>-14.23223962765625</v>
+        <v>-12.11678563734309</v>
       </c>
       <c r="F74">
-        <v>0.1762623538223795</v>
+        <v>1.74392281259836</v>
       </c>
       <c r="G74">
-        <v>-10.33757686250733</v>
+        <v>-7.75822158485835</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.178784874364826</v>
       </c>
       <c r="E75">
-        <v>-14.2886462998958</v>
+        <v>-10.20287138274129</v>
       </c>
       <c r="F75">
-        <v>0.584518258087699</v>
+        <v>1.416860167685837</v>
       </c>
       <c r="G75">
-        <v>-8.891745756413727</v>
+        <v>-8.019996352285141</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.92693283706197</v>
       </c>
       <c r="E76">
-        <v>-13.54793286340917</v>
+        <v>-12.23933067246465</v>
       </c>
       <c r="F76">
-        <v>0.1210599500998204</v>
+        <v>1.204819650121636</v>
       </c>
       <c r="G76">
-        <v>-9.306093636108908</v>
+        <v>-8.101382803822583</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.677209543187969</v>
       </c>
       <c r="E77">
-        <v>-13.82580002851982</v>
+        <v>-11.86017060075043</v>
       </c>
       <c r="F77">
-        <v>0.4202745396650298</v>
+        <v>1.349089773728003</v>
       </c>
       <c r="G77">
-        <v>-7.612256321486345</v>
+        <v>-7.671985184105875</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.429021773148584</v>
       </c>
       <c r="E78">
-        <v>-14.48638664591473</v>
+        <v>-13.16923469604373</v>
       </c>
       <c r="F78">
-        <v>0.3406485514383301</v>
+        <v>1.5675203174374</v>
       </c>
       <c r="G78">
-        <v>-8.807316913525693</v>
+        <v>-7.698916472067846</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.182115281112935</v>
       </c>
       <c r="E79">
-        <v>-16.44759175457863</v>
+        <v>-12.65866736557493</v>
       </c>
       <c r="F79">
-        <v>0.2314481901968825</v>
+        <v>0.8647483235155493</v>
       </c>
       <c r="G79">
-        <v>-7.725003570917303</v>
+        <v>-7.249301350742808</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.93831007178803</v>
       </c>
       <c r="E80">
-        <v>-15.29565212192947</v>
+        <v>-14.36166794326948</v>
       </c>
       <c r="F80">
-        <v>-0.3761460458781101</v>
+        <v>1.182770166593919</v>
       </c>
       <c r="G80">
-        <v>-7.727125630607976</v>
+        <v>-7.830970823083835</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.691646378058969</v>
       </c>
       <c r="E81">
-        <v>-15.76260119075639</v>
+        <v>-14.71293261509646</v>
       </c>
       <c r="F81">
-        <v>-0.02099014886704443</v>
+        <v>1.476403216599065</v>
       </c>
       <c r="G81">
-        <v>-7.666575752694706</v>
+        <v>-6.271343024623325</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.443107669551184</v>
       </c>
       <c r="E82">
-        <v>-18.55870746679245</v>
+        <v>-14.7869369373298</v>
       </c>
       <c r="F82">
-        <v>0.2577753629926564</v>
+        <v>1.137970400715716</v>
       </c>
       <c r="G82">
-        <v>-7.506159958043781</v>
+        <v>-6.686362945062979</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.187494217305816</v>
       </c>
       <c r="E83">
-        <v>-17.69896309101421</v>
+        <v>-16.65445244724901</v>
       </c>
       <c r="F83">
-        <v>-0.2174557025238088</v>
+        <v>1.126240718292075</v>
       </c>
       <c r="G83">
-        <v>-6.583878386803761</v>
+        <v>-6.178233931331323</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.921772527402986</v>
       </c>
       <c r="E84">
-        <v>-19.55634387610425</v>
+        <v>-18.00369316393837</v>
       </c>
       <c r="F84">
-        <v>-0.09049017396192295</v>
+        <v>0.9340528539033672</v>
       </c>
       <c r="G84">
-        <v>-5.866334193894427</v>
+        <v>-5.450175445789264</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.647041948687407</v>
       </c>
       <c r="E85">
-        <v>-20.50479200074474</v>
+        <v>-18.72254312791596</v>
       </c>
       <c r="F85">
-        <v>-0.2375784034726144</v>
+        <v>1.15546220679323</v>
       </c>
       <c r="G85">
-        <v>-6.903170572429849</v>
+        <v>-6.505153613879892</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.362134693556653</v>
       </c>
       <c r="E86">
-        <v>-20.62764044362482</v>
+        <v>-19.5596179628118</v>
       </c>
       <c r="F86">
-        <v>-0.275062028449292</v>
+        <v>1.065155249274834</v>
       </c>
       <c r="G86">
-        <v>-5.944794123175154</v>
+        <v>-6.066830763389308</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.074359706225755</v>
       </c>
       <c r="E87">
-        <v>-23.86170902636471</v>
+        <v>-21.89905933449236</v>
       </c>
       <c r="F87">
-        <v>-0.1711499647073164</v>
+        <v>1.142938948397707</v>
       </c>
       <c r="G87">
-        <v>-5.531773772241221</v>
+        <v>-4.896490014891698</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.7896923253863399</v>
       </c>
       <c r="E88">
-        <v>-23.64079647884853</v>
+        <v>-21.70999101619812</v>
       </c>
       <c r="F88">
-        <v>-0.09796701813959129</v>
+        <v>1.378089259765209</v>
       </c>
       <c r="G88">
-        <v>-5.498847086307629</v>
+        <v>-5.055624628418924</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5165617985934321</v>
       </c>
       <c r="E89">
-        <v>-26.82020638031583</v>
+        <v>-24.32564213150252</v>
       </c>
       <c r="F89">
-        <v>0.07585676929645417</v>
+        <v>1.259089312148643</v>
       </c>
       <c r="G89">
-        <v>-5.337457991268159</v>
+        <v>-5.240703987337419</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2674519637620273</v>
       </c>
       <c r="E90">
-        <v>-27.30249339060673</v>
+        <v>-26.01851251284192</v>
       </c>
       <c r="F90">
-        <v>-0.08516377156192212</v>
+        <v>0.7095404367226171</v>
       </c>
       <c r="G90">
-        <v>-4.876779026750877</v>
+        <v>-3.879844653600291</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.05086632905766236</v>
       </c>
       <c r="E91">
-        <v>-28.23485184709797</v>
+        <v>-27.21689617491375</v>
       </c>
       <c r="F91">
-        <v>-0.2955127628896062</v>
+        <v>0.7818237762909021</v>
       </c>
       <c r="G91">
-        <v>-5.71215215649395</v>
+        <v>-4.650794567149147</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.1215162428183204</v>
       </c>
       <c r="E92">
-        <v>-30.24781288519553</v>
+        <v>-28.46602591671553</v>
       </c>
       <c r="F92">
-        <v>-0.4074533634995146</v>
+        <v>0.6038490397994283</v>
       </c>
       <c r="G92">
-        <v>-5.577167972675706</v>
+        <v>-4.696238425766722</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.239958724475033</v>
       </c>
       <c r="E93">
-        <v>-32.35988636966198</v>
+        <v>-31.16672177388399</v>
       </c>
       <c r="F93">
-        <v>-0.1839648084286248</v>
+        <v>0.7435432618727312</v>
       </c>
       <c r="G93">
-        <v>-5.291881710829013</v>
+        <v>-5.302664157650418</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.2978520270873631</v>
       </c>
       <c r="E94">
-        <v>-34.57351541222443</v>
+        <v>-32.07852095838039</v>
       </c>
       <c r="F94">
-        <v>-0.7341946018597516</v>
+        <v>0.5385720317240216</v>
       </c>
       <c r="G94">
-        <v>-4.924113206871376</v>
+        <v>-4.746873219789875</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2881582320850277</v>
       </c>
       <c r="E95">
-        <v>-36.23073991041245</v>
+        <v>-35.35007624895578</v>
       </c>
       <c r="F95">
-        <v>-0.9414355586921319</v>
+        <v>0.3030771195169558</v>
       </c>
       <c r="G95">
-        <v>-5.891070590163862</v>
+        <v>-5.072756701584653</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.2047411418007706</v>
       </c>
       <c r="E96">
-        <v>-37.82553486593073</v>
+        <v>-37.43942811508874</v>
       </c>
       <c r="F96">
-        <v>-0.9442172164307326</v>
+        <v>-0.06601688741361435</v>
       </c>
       <c r="G96">
-        <v>-6.286571534103972</v>
+        <v>-5.080599383967185</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.05291795976007638</v>
       </c>
       <c r="E97">
-        <v>-40.06964506703881</v>
+        <v>-40.36475892540768</v>
       </c>
       <c r="F97">
-        <v>-1.365323584215681</v>
+        <v>-0.2037462220074769</v>
       </c>
       <c r="G97">
-        <v>-5.932674215955882</v>
+        <v>-5.415649766360205</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1784955672978364</v>
       </c>
       <c r="E98">
-        <v>-44.10274930301011</v>
+        <v>-41.96714813183682</v>
       </c>
       <c r="F98">
-        <v>-1.750488747127964</v>
+        <v>-0.4436231977753522</v>
       </c>
       <c r="G98">
-        <v>-5.784805388898795</v>
+        <v>-4.945598647421246</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4657277300820309</v>
       </c>
       <c r="E99">
-        <v>-45.14841470764726</v>
+        <v>-44.21206213708126</v>
       </c>
       <c r="F99">
-        <v>-2.515798338124163</v>
+        <v>-1.001927088281566</v>
       </c>
       <c r="G99">
-        <v>-6.551825684892537</v>
+        <v>-5.645937935162987</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.8337645792530189</v>
       </c>
       <c r="E100">
-        <v>-47.81983850883014</v>
+        <v>-46.60678938368447</v>
       </c>
       <c r="F100">
-        <v>-2.48977600453262</v>
+        <v>-1.35993505426047</v>
       </c>
       <c r="G100">
-        <v>-6.760704555692852</v>
+        <v>-5.789695064660299</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.228819988207283</v>
       </c>
       <c r="E101">
-        <v>-50.15815115836428</v>
+        <v>-48.72873267725063</v>
       </c>
       <c r="F101">
-        <v>-2.882842135732804</v>
+        <v>-1.324724469437074</v>
       </c>
       <c r="G101">
-        <v>-7.309536726829847</v>
+        <v>-6.48758123815744</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.721142889274705</v>
       </c>
       <c r="E102">
-        <v>-52.24418365304962</v>
+        <v>-51.053009321598</v>
       </c>
       <c r="F102">
-        <v>-2.890509504413117</v>
+        <v>-1.782422310505885</v>
       </c>
       <c r="G102">
-        <v>-7.490848684924652</v>
+        <v>-6.379521721210089</v>
       </c>
     </row>
   </sheetData>
